--- a/tests/TC-07/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-07/results/timetable_all_departments_even.xlsx
@@ -78,14 +78,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0E0E0"/>
-        <bgColor rgb="00E0E0E0"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00E0E0E0"/>
+        <bgColor rgb="00E0E0E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -177,14 +177,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -192,7 +192,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -799,21 +799,35 @@
       <c r="D2" s="8" t="inlineStr"/>
       <c r="E2" s="8" t="inlineStr"/>
       <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="8" t="inlineStr"/>
-      <c r="H2" s="8" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 101
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="11" t="n"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
-      <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="N2" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LAB
+Room: L102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="11" t="n"/>
       <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="8" t="inlineStr"/>
       <c r="T2" s="8" t="inlineStr"/>
@@ -836,21 +850,14 @@
       </c>
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>CS163
-LAB
-Room: L102
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="12" t="n"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -884,19 +891,12 @@
       <c r="D4" s="8" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr"/>
       <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 101
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="n"/>
-      <c r="I4" s="11" t="n"/>
-      <c r="J4" s="12" t="n"/>
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -935,7 +935,7 @@
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -968,18 +968,7 @@
       <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>CS163
 LEC
@@ -987,7 +976,18 @@
 Dr. Vivekraj</t>
         </is>
       </c>
-      <c r="N6" s="12" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
@@ -1069,9 +1069,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="F6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1230,21 +1230,14 @@
       </c>
       <c r="C2" s="8" t="inlineStr"/>
       <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>CS163
-LAB
-Room: L102
-Dr. Hazra</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
-      <c r="J2" s="12" t="n"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1283,25 +1276,25 @@
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="9" t="inlineStr">
         <is>
           <t>CS163
 LEC
-Room: 101
+Room: 102
 Dr. Hazra</t>
         </is>
       </c>
-      <c r="N3" s="12" t="n"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="11" t="n"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
@@ -1329,7 +1322,7 @@
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1368,7 +1361,7 @@
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1401,31 +1394,38 @@
       <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Hazra</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="11" t="n"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="10" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>CS163
-LEC
-Room: 101
+LAB
+Room: L102
 Dr. Hazra</t>
         </is>
       </c>
-      <c r="R6" s="11" t="n"/>
-      <c r="S6" s="12" t="n"/>
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="11" t="n"/>
+      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="R6" s="8" t="inlineStr"/>
+      <c r="S6" s="8" t="inlineStr"/>
       <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
@@ -1496,15 +1496,15 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="Q3:S3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1604,13 +1604,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>L102</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1643,10 +1643,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1676,13 +1676,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1712,13 +1712,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1751,10 +1751,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>L102</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">

--- a/tests/TC-07/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-07/results/timetable_all_departments_even.xlsx
@@ -797,9 +797,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr"/>
       <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="8" t="inlineStr"/>
-      <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>CS163
 LEC
@@ -807,9 +805,11 @@
 Dr. Vivekraj</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="11" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr"/>
       <c r="L2" s="12" t="inlineStr">
         <is>
@@ -817,17 +817,10 @@
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="9" t="inlineStr">
-        <is>
-          <t>CS163
-LAB
-Room: L102
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="11" t="n"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="8" t="inlineStr"/>
+      <c r="Q2" s="8" t="inlineStr"/>
       <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="8" t="inlineStr"/>
       <c r="T2" s="8" t="inlineStr"/>
@@ -863,9 +856,16 @@
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 101
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="11" t="n"/>
       <c r="Q3" s="8" t="inlineStr"/>
       <c r="R3" s="8" t="inlineStr"/>
       <c r="S3" s="8" t="inlineStr"/>
@@ -968,17 +968,10 @@
       <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 101
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="11" t="n"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="12" t="inlineStr">
@@ -987,10 +980,17 @@
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LAB
+Room: L101
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="11" t="n"/>
       <c r="R6" s="8" t="inlineStr"/>
       <c r="S6" s="8" t="inlineStr"/>
       <c r="T6" s="8" t="inlineStr"/>
@@ -1069,9 +1069,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="N6:Q6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1243,9 +1243,16 @@
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
-      <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="8" t="inlineStr"/>
+      <c r="N2" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 101
+Dr. Hazra</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="11" t="n"/>
       <c r="Q2" s="8" t="inlineStr"/>
       <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="8" t="inlineStr"/>
@@ -1281,20 +1288,20 @@
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="9" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>CS163
-LEC
-Room: 102
+LAB
+Room: L101
 Dr. Hazra</t>
         </is>
       </c>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="11" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="11" t="n"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
@@ -1331,9 +1338,16 @@
       <c r="N4" s="8" t="inlineStr"/>
       <c r="O4" s="8" t="inlineStr"/>
       <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="8" t="inlineStr"/>
-      <c r="S4" s="8" t="inlineStr"/>
+      <c r="Q4" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 101
+Dr. Hazra</t>
+        </is>
+      </c>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="11" t="n"/>
       <c r="T4" s="8" t="inlineStr"/>
       <c r="U4" s="7" t="inlineStr">
         <is>
@@ -1394,17 +1408,10 @@
       <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 102
-Dr. Hazra</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="11" t="n"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="12" t="inlineStr">
@@ -1412,17 +1419,10 @@
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>CS163
-LAB
-Room: L102
-Dr. Hazra</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="n"/>
-      <c r="O6" s="10" t="n"/>
-      <c r="P6" s="11" t="n"/>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
       <c r="R6" s="8" t="inlineStr"/>
       <c r="S6" s="8" t="inlineStr"/>
@@ -1496,15 +1496,15 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="M6:P6"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q4:S4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1571,10 +1571,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1604,13 +1604,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1643,10 +1643,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>L101</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1676,13 +1676,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1712,13 +1712,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>L101</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
